--- a/test1.xlsx
+++ b/test1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Automated-recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AEC2B3-CD8A-4DF0-BC78-6C57711235F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F55564A-BD45-4E0F-861B-B67CD94A8698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1D30F33-C917-4DB8-AB4B-FBD71EBDB54C}"/>
+    <workbookView xWindow="36" yWindow="744" windowWidth="23004" windowHeight="12216" xr2:uid="{C1D30F33-C917-4DB8-AB4B-FBD71EBDB54C}"/>
   </bookViews>
   <sheets>
     <sheet name="Output File" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="348">
   <si>
     <t>Account-No</t>
   </si>
@@ -78,9 +78,6 @@
     <t>PETTY CASH 16-31 DESEMBER 2026</t>
   </si>
   <si>
-    <t>ONGKOS KIRIM CROWN 221225</t>
-  </si>
-  <si>
     <t>PAMERAN WEDDING 30 JANUARI 2026</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>BIAYA KEAMANAN DES 2025</t>
   </si>
   <si>
-    <t>BIAYA HAMPERS COOKIES 10 BOX TO GOLDEN FLOWER</t>
-  </si>
-  <si>
     <t>JV-ASTCA 019</t>
   </si>
   <si>
@@ -189,9 +183,6 @@
     <t>JV-ASTCA 024</t>
   </si>
   <si>
-    <t>TRASNFER HAMPER FROM SERELA CIHAMPELAS</t>
-  </si>
-  <si>
     <t>JV-ASTCA 037</t>
   </si>
   <si>
@@ -207,21 +198,12 @@
     <t>JV-ASTCA 011</t>
   </si>
   <si>
-    <t>PEMBELIAN HARDWARE KOMPUTER HK (DYTECH)</t>
-  </si>
-  <si>
-    <t>PEMBELIAN 1 UNIT POWER SUPPLY HK (ZEUS)</t>
-  </si>
-  <si>
     <t>JV-ASTCA 012</t>
   </si>
   <si>
     <t>PEMBELIAN FILTER (2 UNIT) ARIA WATER FILTER</t>
   </si>
   <si>
-    <t>PEMBELIAN POMPA AIR (2 UNIT) GUMBIRA</t>
-  </si>
-  <si>
     <t>APM-02/26-04</t>
   </si>
   <si>
@@ -414,9 +396,6 @@
     <t>PROJECT PEMBELIAN VACUUM HK ( 3 UNIT )</t>
   </si>
   <si>
-    <t>BIAYA PENGURUSAN IPAT GINO FERUCI KEBONJATI</t>
-  </si>
-  <si>
     <t>APP-110326</t>
   </si>
   <si>
@@ -432,9 +411,6 @@
     <t>PNH - PEMBELIAN CCTV FO</t>
   </si>
   <si>
-    <t>IURAN IPAT HOTEL GINO FERUCI KEBONJATI</t>
-  </si>
-  <si>
     <t>PROJECT PENGGANTIAN KERAMIK MUSHOLLA ( TB LAY )</t>
   </si>
   <si>
@@ -489,9 +465,6 @@
     <t>PROJECT PENGGANTIAN KERAMIK MUSHOLLA (TB LAY)</t>
   </si>
   <si>
-    <t>PELUNASAN BATH TOWEL &amp; BATH MAT 664 PCS (PT WONDERFUL INDAH</t>
-  </si>
-  <si>
     <t>PEMBELIAN INVERTER ( 1 UNIT ) RBCA 11/15 KW</t>
   </si>
   <si>
@@ -543,15 +516,6 @@
     <t>JV-ASTCA 046</t>
   </si>
   <si>
-    <t>PROJECT RENOVASI MEETING ROOM KEBON KARET ( PT. HATSON SURYA</t>
-  </si>
-  <si>
-    <t>PROJECT RENOVASI MEETING ROOM KEBON KARET ( WARGA RAMA )</t>
-  </si>
-  <si>
-    <t>PROJECT RENOVASI MEETING ROOM KEBON KARET ( PANCA MAKMUR )</t>
-  </si>
-  <si>
     <t>PEMBELIAN POMPA</t>
   </si>
   <si>
@@ -624,9 +588,6 @@
     <t>BIAYA SEDOT BIOTEK</t>
   </si>
   <si>
-    <t>PEMBELIAN PCB AC BALLROOM &amp; KEBONJATI</t>
-  </si>
-  <si>
     <t>ADJ 010426-01</t>
   </si>
   <si>
@@ -648,9 +609,6 @@
     <t>ARP-030426-MDR</t>
   </si>
   <si>
-    <t>DP RENOVASI GEDUNG KE AJAT SUDRAJAT_030426</t>
-  </si>
-  <si>
     <t>ARP-060426-MDR</t>
   </si>
   <si>
@@ -678,12 +636,6 @@
     <t>ARP-070426-MDR</t>
   </si>
   <si>
-    <t>PEMBELIAN GRANIT MEETING ROOM KE NOVA TRISNAWATY_070426</t>
-  </si>
-  <si>
-    <t>PEMBELIAN AC PROJECT RENOVASI MEETING ROOM  KE HATSONSURYA E</t>
-  </si>
-  <si>
     <t>JV-CA 0426-01</t>
   </si>
   <si>
@@ -717,12 +669,6 @@
     <t>ARP-100426-MDR</t>
   </si>
   <si>
-    <t>PEMBELIAN INFOKUS 2 UNIT KE ANGGI PRATIWI_100426</t>
-  </si>
-  <si>
-    <t>PEMBELIAN HAMPERS 5BOX SERELA CIHAMPELAS_100426</t>
-  </si>
-  <si>
     <t>JV-CA 0426-10</t>
   </si>
   <si>
@@ -732,9 +678,6 @@
     <t>JV-CA 0426-11</t>
   </si>
   <si>
-    <t>SHARING BUKA PUASA PHRI BERSAMA ANAK YATIM 9 MARET 2026</t>
-  </si>
-  <si>
     <t>JV-CA 0426-12</t>
   </si>
   <si>
@@ -759,9 +702,6 @@
     <t>ARP-150426-MDR</t>
   </si>
   <si>
-    <t>PEMBELIAN BATU TAMAN KE ENGKOS KOSWARA_150426</t>
-  </si>
-  <si>
     <t>DLHK APRIL 2026_150426</t>
   </si>
   <si>
@@ -810,15 +750,9 @@
     <t>JV-CA 0426-20</t>
   </si>
   <si>
-    <t>ALARIC BE SUBSCRIPTIONS MARET 2026</t>
-  </si>
-  <si>
     <t>JV-CA 0426-23</t>
   </si>
   <si>
-    <t>ALARIC BE SUBSCRIPTIONS APRIL 2026</t>
-  </si>
-  <si>
     <t>JV-CA 0426-24</t>
   </si>
   <si>
@@ -831,9 +765,6 @@
     <t>ARP-280426-MDR</t>
   </si>
   <si>
-    <t>SHARING BUKA PUASA PHRI BERSAMA ANAK YATIM 9 MARET 2026_2804</t>
-  </si>
-  <si>
     <t>ARP-290426-MDR</t>
   </si>
   <si>
@@ -855,9 +786,6 @@
     <t>ARP-300426-MDR</t>
   </si>
   <si>
-    <t>TERM 2 DESIGN INTERIOR MARK STUDIO KE ADWIN ADHYNATA_300426</t>
-  </si>
-  <si>
     <t>JB-0426-01</t>
   </si>
   <si>
@@ -891,9 +819,6 @@
     <t>JV-CA 0526-03</t>
   </si>
   <si>
-    <t>AC SERVER 2PK (SEJAHYA)</t>
-  </si>
-  <si>
     <t>JV-CA 0526-04</t>
   </si>
   <si>
@@ -915,9 +840,6 @@
     <t>JV-CA 0526-05</t>
   </si>
   <si>
-    <t>GOLDEN FLOWER - SURABAYA BUSINESS MATCHING TGL 19-21 MEI 202</t>
-  </si>
-  <si>
     <t>JV-CA 0526-07</t>
   </si>
   <si>
@@ -927,15 +849,9 @@
     <t>JV-CA 0526-10</t>
   </si>
   <si>
-    <t>PROJECT RENOVASI GEDUNG KEBON KARET</t>
-  </si>
-  <si>
     <t>JV-CA 0526-11</t>
   </si>
   <si>
-    <t>PROJECT RENOVASI GEDUNG HERITAGE TERMIN 1 / DP (REVAN JAYA)</t>
-  </si>
-  <si>
     <t>JV-CA 0526-12</t>
   </si>
   <si>
@@ -963,9 +879,6 @@
     <t>ARP-130526-MDR</t>
   </si>
   <si>
-    <t>PEMEBLIAN PAKET SOUND SYSTEM GINO FERUCI KEBON JATI _130526</t>
-  </si>
-  <si>
     <t>PROJECT PEMBELIAN AC SERVER 2PK &amp; PEMASANGAN (SEJAHYA)1UNIT_</t>
   </si>
   <si>
@@ -1026,18 +939,12 @@
     <t>PEMBELIAN SUGAR BOWL HK 240426</t>
   </si>
   <si>
-    <t>PEMBELIAN SAMPLING PACKAGING FERUCI COFFEE SHOP 270426</t>
-  </si>
-  <si>
     <t>PEMBELIAN TIMBANGAN 40 KG &amp; 150 UNTUK KITCHEN &amp; STORE 210526</t>
   </si>
   <si>
     <t>ARP-250526-MDR</t>
   </si>
   <si>
-    <t>ALARIC BE SUBSCRIPTIONS MEI 2026_250526</t>
-  </si>
-  <si>
     <t>ARP-260526-MDR</t>
   </si>
   <si>
@@ -1059,9 +966,6 @@
     <t>APM-05/26-06</t>
   </si>
   <si>
-    <t>OWNER EXPENSES APRIL-MEI 2026</t>
-  </si>
-  <si>
     <t>JV-CA 0526-60</t>
   </si>
   <si>
@@ -1069,6 +973,108 @@
   </si>
   <si>
     <t>Opening balance</t>
+  </si>
+  <si>
+    <t>SURABAYA BUSINESS MATCHING TGL 19-21 MEI 202</t>
+  </si>
+  <si>
+    <t>SUBSCRIPTIONS MEI 2026_250526</t>
+  </si>
+  <si>
+    <t>EXPENSES APRIL-MEI 2026</t>
+  </si>
+  <si>
+    <t>PEMBELIAN SAMPLING PACKAGING COFFEE SHOP 270426</t>
+  </si>
+  <si>
+    <t>PEMEBLIAN PAKET SOUND SYSTEM _130526</t>
+  </si>
+  <si>
+    <t>ONGKOS KIRIM 160426</t>
+  </si>
+  <si>
+    <t>PROJECT RENOVASI GEDUNG TERMIN 1 / DP (REVAN JAYA)</t>
+  </si>
+  <si>
+    <t>PROJECT RENOVASI GEDUNG</t>
+  </si>
+  <si>
+    <t>AC SERVER 2PK</t>
+  </si>
+  <si>
+    <t>TERM 2 DESIGN INTERIOR MARK STUDIO_300426</t>
+  </si>
+  <si>
+    <t>SHARING BUKA PUASA PHRI BERSAMA ANAK YATIM_2804</t>
+  </si>
+  <si>
+    <t>SUBSCRIPTIONS APRIL 2026</t>
+  </si>
+  <si>
+    <t>SUBSCRIPTIONS MARET 2026</t>
+  </si>
+  <si>
+    <t>PEMBELIAN BATU TAMAN_150426</t>
+  </si>
+  <si>
+    <t>SHARING BUKA PUASA PHRI BERSAMA ANAK YATIM</t>
+  </si>
+  <si>
+    <t>PEMBELIAN HAMPERS 5BOX_100426</t>
+  </si>
+  <si>
+    <t>PEMBELIAN INFOKUS 2 UNIT_100426</t>
+  </si>
+  <si>
+    <t>PEMBELIAN AC PROJECT RENOVASI MEETING ROOM</t>
+  </si>
+  <si>
+    <t>PEMBELIAN GRANIT MEETING ROOM_070426</t>
+  </si>
+  <si>
+    <t>DP RENOVASI GEDUNG_030426</t>
+  </si>
+  <si>
+    <t>PEMBELIAN PCB AC BALLROOM</t>
+  </si>
+  <si>
+    <t>PROJECT RENOVASI MEETING ROOM ( WARGA RAMA )</t>
+  </si>
+  <si>
+    <t>PROJECT RENOVASI MEETING ROOM ( PANCA MAKMUR )</t>
+  </si>
+  <si>
+    <t>PROJECT RENOVASI MEETING ROOM ( PT. HATSON SURYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PELUNASAN BATH TOWEL &amp; BATH MAT 664 PCS </t>
+  </si>
+  <si>
+    <t>IURAN IPAT</t>
+  </si>
+  <si>
+    <t>BIAYA PENGURUSAN IPAT</t>
+  </si>
+  <si>
+    <t>ONGKOS KIRIM 060226</t>
+  </si>
+  <si>
+    <t>PEMBELIAN POMPA AIR (2 UNIT)</t>
+  </si>
+  <si>
+    <t>PEMBELIAN 1 UNIT POWER SUPPLY HK</t>
+  </si>
+  <si>
+    <t>PEMBELIAN HARDWARE KOMPUTER HK</t>
+  </si>
+  <si>
+    <t>TRASNFER HAMPER</t>
+  </si>
+  <si>
+    <t>BIAYA HAMPERS COOKIES 10 BOX</t>
+  </si>
+  <si>
+    <t>ONGKOS KIRIM 221225</t>
   </si>
 </sst>
 </file>
@@ -1948,7 +1954,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2078,7 +2084,7 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>347</v>
       </c>
       <c r="F7" s="2">
         <v>192800</v>
@@ -2104,7 +2110,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2">
         <v>119000</v>
@@ -2127,10 +2133,10 @@
         <v>46037</v>
       </c>
       <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
         <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2153,10 +2159,10 @@
         <v>46037</v>
       </c>
       <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2179,10 +2185,10 @@
         <v>46037</v>
       </c>
       <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
         <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2205,10 +2211,10 @@
         <v>46037</v>
       </c>
       <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
         <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
       </c>
       <c r="F12" s="2">
         <v>567987</v>
@@ -2231,10 +2237,10 @@
         <v>46037</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="2">
         <v>565440</v>
@@ -2257,10 +2263,10 @@
         <v>46037</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="2">
         <v>915900</v>
@@ -2283,10 +2289,10 @@
         <v>46037</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="2">
         <v>1295128</v>
@@ -2309,10 +2315,10 @@
         <v>46043</v>
       </c>
       <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
         <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2335,10 +2341,10 @@
         <v>46044</v>
       </c>
       <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
         <v>30</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
       </c>
       <c r="F17" s="2">
         <v>600000</v>
@@ -2361,10 +2367,10 @@
         <v>46044</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>346</v>
       </c>
       <c r="F18" s="2">
         <v>1500000</v>
@@ -2387,10 +2393,10 @@
         <v>46044</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2413,10 +2419,10 @@
         <v>46045</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F20" s="2">
         <v>5000000</v>
@@ -2439,10 +2445,10 @@
         <v>46048</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2465,10 +2471,10 @@
         <v>46049</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2491,10 +2497,10 @@
         <v>46051</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2517,10 +2523,10 @@
         <v>46052</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F24" s="2">
         <v>1500000</v>
@@ -2543,10 +2549,10 @@
         <v>46052</v>
       </c>
       <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" t="s">
         <v>43</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
       </c>
       <c r="F25" s="2">
         <v>720000</v>
@@ -2569,10 +2575,10 @@
         <v>46052</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F26" s="2">
         <v>17297626</v>
@@ -2595,10 +2601,10 @@
         <v>46053</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2621,10 +2627,10 @@
         <v>46053</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2647,10 +2653,10 @@
         <v>46053</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>345</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2673,10 +2679,10 @@
         <v>46053</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2699,10 +2705,10 @@
         <v>46053</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2725,10 +2731,10 @@
         <v>46054</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>344</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2751,10 +2757,10 @@
         <v>46054</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>343</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2777,10 +2783,10 @@
         <v>46054</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2803,10 +2809,10 @@
         <v>46054</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>62</v>
+        <v>342</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2829,10 +2835,10 @@
         <v>46059</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>341</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2855,10 +2861,10 @@
         <v>46063</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F37" s="2">
         <v>395000</v>
@@ -2881,10 +2887,10 @@
         <v>46063</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F38" s="2">
         <v>2400000</v>
@@ -2907,10 +2913,10 @@
         <v>46063</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F39" s="2">
         <v>800000</v>
@@ -2933,10 +2939,10 @@
         <v>46063</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F40" s="2">
         <v>5400000</v>
@@ -2959,10 +2965,10 @@
         <v>46065</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F41" s="2">
         <v>640000</v>
@@ -2985,10 +2991,10 @@
         <v>46066</v>
       </c>
       <c r="D42" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F42" s="2">
         <v>1800000</v>
@@ -3011,10 +3017,10 @@
         <v>46066</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F43" s="2">
         <v>44689266</v>
@@ -3037,10 +3043,10 @@
         <v>46066</v>
       </c>
       <c r="D44" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F44" s="2">
         <v>2619000</v>
@@ -3063,10 +3069,10 @@
         <v>46066</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3089,10 +3095,10 @@
         <v>46066</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3115,10 +3121,10 @@
         <v>46066</v>
       </c>
       <c r="D47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -3141,10 +3147,10 @@
         <v>46068</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -3167,10 +3173,10 @@
         <v>46068</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -3193,10 +3199,10 @@
         <v>46068</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E50" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -3219,10 +3225,10 @@
         <v>46068</v>
       </c>
       <c r="D51" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -3245,10 +3251,10 @@
         <v>46068</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E52" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -3271,10 +3277,10 @@
         <v>46068</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3297,10 +3303,10 @@
         <v>46068</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3323,10 +3329,10 @@
         <v>46068</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E55" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F55" s="2">
         <v>627600</v>
@@ -3349,10 +3355,10 @@
         <v>46068</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E56" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F56" s="2">
         <v>1830386</v>
@@ -3375,10 +3381,10 @@
         <v>46068</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -3401,10 +3407,10 @@
         <v>46068</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F58" s="2">
         <v>600000</v>
@@ -3427,10 +3433,10 @@
         <v>46073</v>
       </c>
       <c r="D59" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F59" s="2">
         <v>26400000</v>
@@ -3453,10 +3459,10 @@
         <v>46078</v>
       </c>
       <c r="D60" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3479,10 +3485,10 @@
         <v>46078</v>
       </c>
       <c r="D61" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3505,10 +3511,10 @@
         <v>46080</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F62" s="2">
         <v>2025000</v>
@@ -3531,10 +3537,10 @@
         <v>46081</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E63" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3557,10 +3563,10 @@
         <v>46081</v>
       </c>
       <c r="D64" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3583,10 +3589,10 @@
         <v>46081</v>
       </c>
       <c r="D65" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E65" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3609,10 +3615,10 @@
         <v>46081</v>
       </c>
       <c r="D66" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E66" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3635,10 +3641,10 @@
         <v>46081</v>
       </c>
       <c r="D67" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3661,10 +3667,10 @@
         <v>46081</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E68" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F68" s="2">
         <v>529823</v>
@@ -3687,10 +3693,10 @@
         <v>46081</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E69" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3713,10 +3719,10 @@
         <v>46082</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E70" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3739,10 +3745,10 @@
         <v>46082</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E71" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -3765,10 +3771,10 @@
         <v>46083</v>
       </c>
       <c r="D72" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E72" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F72" s="2">
         <v>27152154</v>
@@ -3791,10 +3797,10 @@
         <v>46083</v>
       </c>
       <c r="D73" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E73" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F73" s="2">
         <v>1831500</v>
@@ -3817,10 +3823,10 @@
         <v>46083</v>
       </c>
       <c r="D74" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E74" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F74" s="2">
         <v>22000000</v>
@@ -3843,10 +3849,10 @@
         <v>46084</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3869,10 +3875,10 @@
         <v>46086</v>
       </c>
       <c r="D76" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E76" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F76" s="2">
         <v>777000</v>
@@ -3895,10 +3901,10 @@
         <v>46086</v>
       </c>
       <c r="D77" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E77" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F77" s="2">
         <v>675000</v>
@@ -3921,10 +3927,10 @@
         <v>46086</v>
       </c>
       <c r="D78" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E78" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3947,10 +3953,10 @@
         <v>46087</v>
       </c>
       <c r="D79" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E79" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F79" s="2">
         <v>5000000</v>
@@ -3973,10 +3979,10 @@
         <v>46087</v>
       </c>
       <c r="D80" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E80" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F80" s="2">
         <v>2970500</v>
@@ -3999,10 +4005,10 @@
         <v>46090</v>
       </c>
       <c r="D81" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F81" s="2">
         <v>104274954</v>
@@ -4025,10 +4031,10 @@
         <v>46090</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F82" s="2">
         <v>3683000</v>
@@ -4051,10 +4057,10 @@
         <v>46090</v>
       </c>
       <c r="D83" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F83" s="2">
         <v>1455000</v>
@@ -4077,10 +4083,10 @@
         <v>46090</v>
       </c>
       <c r="D84" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4103,10 +4109,10 @@
         <v>46090</v>
       </c>
       <c r="D85" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E85" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4129,10 +4135,10 @@
         <v>46090</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E86" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4155,10 +4161,10 @@
         <v>46091</v>
       </c>
       <c r="D87" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E87" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4181,10 +4187,10 @@
         <v>46091</v>
       </c>
       <c r="D88" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E88" t="s">
-        <v>127</v>
+        <v>340</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4207,10 +4213,10 @@
         <v>46092</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E89" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F89" s="2">
         <v>3025000</v>
@@ -4233,10 +4239,10 @@
         <v>46092</v>
       </c>
       <c r="D90" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F90" s="2">
         <v>5500000</v>
@@ -4259,10 +4265,10 @@
         <v>46092</v>
       </c>
       <c r="D91" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E91" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -4285,10 +4291,10 @@
         <v>46093</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F92" s="2">
         <v>1221000</v>
@@ -4311,10 +4317,10 @@
         <v>46093</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E93" t="s">
-        <v>133</v>
+        <v>339</v>
       </c>
       <c r="F93" s="2">
         <v>12272727</v>
@@ -4337,10 +4343,10 @@
         <v>46093</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E94" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4363,10 +4369,10 @@
         <v>46093</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E95" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4389,10 +4395,10 @@
         <v>46093</v>
       </c>
       <c r="D96" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E96" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F96" s="2">
         <v>23333</v>
@@ -4415,10 +4421,10 @@
         <v>46093</v>
       </c>
       <c r="D97" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E97" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -4441,10 +4447,10 @@
         <v>46094</v>
       </c>
       <c r="D98" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E98" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F98" s="2">
         <v>12903612</v>
@@ -4467,10 +4473,10 @@
         <v>46094</v>
       </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E99" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F99" s="2">
         <v>920000</v>
@@ -4493,10 +4499,10 @@
         <v>46096</v>
       </c>
       <c r="D100" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E100" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -4519,10 +4525,10 @@
         <v>46097</v>
       </c>
       <c r="D101" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E101" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F101" s="2">
         <v>5070885</v>
@@ -4545,10 +4551,10 @@
         <v>46097</v>
       </c>
       <c r="D102" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E102" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4571,10 +4577,10 @@
         <v>46098</v>
       </c>
       <c r="D103" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E103" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F103" s="2">
         <v>5427000</v>
@@ -4597,10 +4603,10 @@
         <v>46098</v>
       </c>
       <c r="D104" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E104" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F104" s="2">
         <v>4401463</v>
@@ -4623,10 +4629,10 @@
         <v>46098</v>
       </c>
       <c r="D105" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E105" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F105" s="2">
         <v>2261500</v>
@@ -4649,10 +4655,10 @@
         <v>46098</v>
       </c>
       <c r="D106" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E106" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F106" s="2">
         <v>660000</v>
@@ -4675,10 +4681,10 @@
         <v>46098</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E107" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F107" s="2">
         <v>2430000</v>
@@ -4701,10 +4707,10 @@
         <v>46098</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E108" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F108" s="2">
         <v>665000</v>
@@ -4727,10 +4733,10 @@
         <v>46098</v>
       </c>
       <c r="D109" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E109" t="s">
-        <v>152</v>
+        <v>338</v>
       </c>
       <c r="F109" s="2">
         <v>26609111</v>
@@ -4753,10 +4759,10 @@
         <v>46101</v>
       </c>
       <c r="D110" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E110" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -4779,10 +4785,10 @@
         <v>46105</v>
       </c>
       <c r="D111" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E111" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -4805,10 +4811,10 @@
         <v>46105</v>
       </c>
       <c r="D112" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E112" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -4831,10 +4837,10 @@
         <v>46105</v>
       </c>
       <c r="D113" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E113" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -4857,10 +4863,10 @@
         <v>46105</v>
       </c>
       <c r="D114" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E114" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -4883,10 +4889,10 @@
         <v>46105</v>
       </c>
       <c r="D115" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E115" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -4909,10 +4915,10 @@
         <v>46105</v>
       </c>
       <c r="D116" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E116" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -4935,10 +4941,10 @@
         <v>46105</v>
       </c>
       <c r="D117" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E117" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -4961,10 +4967,10 @@
         <v>46105</v>
       </c>
       <c r="D118" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E118" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -4987,10 +4993,10 @@
         <v>46105</v>
       </c>
       <c r="D119" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E119" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -5013,10 +5019,10 @@
         <v>46105</v>
       </c>
       <c r="D120" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E120" t="s">
-        <v>170</v>
+        <v>337</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -5039,10 +5045,10 @@
         <v>46105</v>
       </c>
       <c r="D121" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E121" t="s">
-        <v>171</v>
+        <v>335</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -5065,10 +5071,10 @@
         <v>46105</v>
       </c>
       <c r="D122" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E122" t="s">
-        <v>172</v>
+        <v>336</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -5091,10 +5097,10 @@
         <v>46105</v>
       </c>
       <c r="D123" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E123" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F123" s="2">
         <v>1200000</v>
@@ -5117,10 +5123,10 @@
         <v>46105</v>
       </c>
       <c r="D124" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E124" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F124" s="2">
         <v>1407500</v>
@@ -5143,10 +5149,10 @@
         <v>46105</v>
       </c>
       <c r="D125" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E125" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F125" s="2">
         <v>800000</v>
@@ -5169,10 +5175,10 @@
         <v>46105</v>
       </c>
       <c r="D126" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E126" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F126" s="2">
         <v>409500</v>
@@ -5195,10 +5201,10 @@
         <v>46105</v>
       </c>
       <c r="D127" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E127" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F127" s="2">
         <v>777000</v>
@@ -5221,10 +5227,10 @@
         <v>46105</v>
       </c>
       <c r="D128" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E128" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F128" s="2">
         <v>1255200</v>
@@ -5247,10 +5253,10 @@
         <v>46105</v>
       </c>
       <c r="D129" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E129" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F129" s="2">
         <v>539251</v>
@@ -5273,10 +5279,10 @@
         <v>46105</v>
       </c>
       <c r="D130" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E130" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F130" s="2">
         <v>524500</v>
@@ -5299,10 +5305,10 @@
         <v>46108</v>
       </c>
       <c r="D131" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E131" t="s">
-        <v>171</v>
+        <v>335</v>
       </c>
       <c r="F131" s="2">
         <v>800000</v>
@@ -5325,10 +5331,10 @@
         <v>46108</v>
       </c>
       <c r="D132" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E132" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F132" s="2">
         <v>8500000</v>
@@ -5351,10 +5357,10 @@
         <v>46108</v>
       </c>
       <c r="D133" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E133" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F133" s="2">
         <v>2958000</v>
@@ -5377,10 +5383,10 @@
         <v>46108</v>
       </c>
       <c r="D134" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E134" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F134" s="2">
         <v>2800000</v>
@@ -5403,10 +5409,10 @@
         <v>46111</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E135" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -5429,10 +5435,10 @@
         <v>46111</v>
       </c>
       <c r="D136" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E136" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -5455,10 +5461,10 @@
         <v>46111</v>
       </c>
       <c r="D137" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E137" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -5481,10 +5487,10 @@
         <v>46112</v>
       </c>
       <c r="D138" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E138" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -5507,10 +5513,10 @@
         <v>46112</v>
       </c>
       <c r="D139" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E139" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -5533,10 +5539,10 @@
         <v>46112</v>
       </c>
       <c r="D140" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E140" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F140" s="2">
         <v>11737877</v>
@@ -5559,10 +5565,10 @@
         <v>46112</v>
       </c>
       <c r="D141" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E141" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -5585,10 +5591,10 @@
         <v>46112</v>
       </c>
       <c r="D142" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E142" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F142" s="2">
         <v>1020600</v>
@@ -5611,10 +5617,10 @@
         <v>46112</v>
       </c>
       <c r="D143" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E143" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F143" s="2">
         <v>800000</v>
@@ -5637,10 +5643,10 @@
         <v>46112</v>
       </c>
       <c r="D144" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E144" t="s">
-        <v>197</v>
+        <v>334</v>
       </c>
       <c r="F144" s="2">
         <v>600000</v>
@@ -5663,10 +5669,10 @@
         <v>46113</v>
       </c>
       <c r="D145" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="F145" s="2">
         <v>730239</v>
@@ -5689,10 +5695,10 @@
         <v>46113</v>
       </c>
       <c r="D146" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E146" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -5715,10 +5721,10 @@
         <v>46113</v>
       </c>
       <c r="D147" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E147" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -5741,10 +5747,10 @@
         <v>46115</v>
       </c>
       <c r="D148" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E148" t="s">
-        <v>205</v>
+        <v>333</v>
       </c>
       <c r="F148" s="2">
         <v>150000000</v>
@@ -5767,10 +5773,10 @@
         <v>46118</v>
       </c>
       <c r="D149" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="E149" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="F149" s="2">
         <v>4292996</v>
@@ -5793,10 +5799,10 @@
         <v>46118</v>
       </c>
       <c r="D150" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E150" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -5819,10 +5825,10 @@
         <v>46118</v>
       </c>
       <c r="D151" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="E151" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -5845,10 +5851,10 @@
         <v>46118</v>
       </c>
       <c r="D152" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="E152" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -5871,10 +5877,10 @@
         <v>46119</v>
       </c>
       <c r="D153" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E153" t="s">
-        <v>215</v>
+        <v>332</v>
       </c>
       <c r="F153" s="2">
         <v>4810000</v>
@@ -5897,10 +5903,10 @@
         <v>46119</v>
       </c>
       <c r="D154" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E154" t="s">
-        <v>216</v>
+        <v>331</v>
       </c>
       <c r="F154" s="2">
         <v>5916000</v>
@@ -5923,10 +5929,10 @@
         <v>46119</v>
       </c>
       <c r="D155" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E155" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="F155" s="2">
         <v>10000000</v>
@@ -5949,10 +5955,10 @@
         <v>46119</v>
       </c>
       <c r="D156" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E156" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -5975,10 +5981,10 @@
         <v>46119</v>
       </c>
       <c r="D157" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E157" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -6001,10 +6007,10 @@
         <v>46119</v>
       </c>
       <c r="D158" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E158" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6027,10 +6033,10 @@
         <v>46120</v>
       </c>
       <c r="D159" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="E159" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -6053,10 +6059,10 @@
         <v>46121</v>
       </c>
       <c r="D160" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="E160" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -6079,10 +6085,10 @@
         <v>46122</v>
       </c>
       <c r="D161" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E161" t="s">
-        <v>228</v>
+        <v>330</v>
       </c>
       <c r="F161" s="2">
         <v>13800000</v>
@@ -6105,10 +6111,10 @@
         <v>46122</v>
       </c>
       <c r="D162" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E162" t="s">
-        <v>229</v>
+        <v>329</v>
       </c>
       <c r="F162" s="2">
         <v>300000</v>
@@ -6131,10 +6137,10 @@
         <v>46123</v>
       </c>
       <c r="D163" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="E163" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -6157,10 +6163,10 @@
         <v>46125</v>
       </c>
       <c r="D164" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="E164" t="s">
-        <v>233</v>
+        <v>328</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -6183,10 +6189,10 @@
         <v>46125</v>
       </c>
       <c r="D165" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="E165" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="F165" s="2">
         <v>500000</v>
@@ -6209,10 +6215,10 @@
         <v>46125</v>
       </c>
       <c r="D166" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="E166" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="F166" s="2">
         <v>739000</v>
@@ -6235,10 +6241,10 @@
         <v>46125</v>
       </c>
       <c r="D167" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="E167" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="F167" s="2">
         <v>1800000</v>
@@ -6261,10 +6267,10 @@
         <v>46125</v>
       </c>
       <c r="D168" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="E168" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="F168" s="2">
         <v>1341600</v>
@@ -6287,10 +6293,10 @@
         <v>46126</v>
       </c>
       <c r="D169" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="E169" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="F169" s="2">
         <v>2156250</v>
@@ -6313,10 +6319,10 @@
         <v>46127</v>
       </c>
       <c r="D170" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="E170" t="s">
-        <v>242</v>
+        <v>327</v>
       </c>
       <c r="F170" s="2">
         <v>1075000</v>
@@ -6339,10 +6345,10 @@
         <v>46127</v>
       </c>
       <c r="D171" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="E171" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="F171" s="2">
         <v>409500</v>
@@ -6365,10 +6371,10 @@
         <v>46127</v>
       </c>
       <c r="D172" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="E172" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F172" s="2">
         <v>203800</v>
@@ -6391,10 +6397,10 @@
         <v>46128</v>
       </c>
       <c r="D173" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="E173" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -6417,10 +6423,10 @@
         <v>46128</v>
       </c>
       <c r="D174" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="E174" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="F174" s="2">
         <v>810000</v>
@@ -6443,10 +6449,10 @@
         <v>46129</v>
       </c>
       <c r="D175" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E175" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -6469,10 +6475,10 @@
         <v>46129</v>
       </c>
       <c r="D176" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E176" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -6495,10 +6501,10 @@
         <v>46131</v>
       </c>
       <c r="D177" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E177" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -6521,10 +6527,10 @@
         <v>46133</v>
       </c>
       <c r="D178" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="E178" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="F178" s="2">
         <v>1200000</v>
@@ -6547,10 +6553,10 @@
         <v>46133</v>
       </c>
       <c r="D179" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="E179" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="F179" s="2">
         <v>2430000</v>
@@ -6573,10 +6579,10 @@
         <v>46133</v>
       </c>
       <c r="D180" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E180" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -6599,10 +6605,10 @@
         <v>46134</v>
       </c>
       <c r="D181" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="E181" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -6625,10 +6631,10 @@
         <v>46134</v>
       </c>
       <c r="D182" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="E182" t="s">
-        <v>261</v>
+        <v>325</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -6651,10 +6657,10 @@
         <v>46135</v>
       </c>
       <c r="D183" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="E183" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -6677,10 +6683,10 @@
         <v>46136</v>
       </c>
       <c r="D184" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="E184" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="F184" s="2">
         <v>2952761</v>
@@ -6703,10 +6709,10 @@
         <v>46140</v>
       </c>
       <c r="D185" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="E185" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="F185" s="2">
         <v>1000000</v>
@@ -6729,10 +6735,10 @@
         <v>46141</v>
       </c>
       <c r="D186" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="E186" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F186" s="2">
         <v>13888862</v>
@@ -6755,10 +6761,10 @@
         <v>46141</v>
       </c>
       <c r="D187" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="E187" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="F187" s="2">
         <v>1470000</v>
@@ -6781,10 +6787,10 @@
         <v>46141</v>
       </c>
       <c r="D188" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="E188" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="F188" s="2">
         <v>1470000</v>
@@ -6807,10 +6813,10 @@
         <v>46142</v>
       </c>
       <c r="D189" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="E189" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -6833,10 +6839,10 @@
         <v>46142</v>
       </c>
       <c r="D190" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="E190" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
       <c r="F190" s="2">
         <v>35200000</v>
@@ -6859,10 +6865,10 @@
         <v>46142</v>
       </c>
       <c r="D191" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="E191" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="F191" s="2">
         <v>12903612</v>
@@ -6885,10 +6891,10 @@
         <v>46142</v>
       </c>
       <c r="D192" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="E192" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -6911,10 +6917,10 @@
         <v>46142</v>
       </c>
       <c r="D193" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="E193" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -6937,10 +6943,10 @@
         <v>46143</v>
       </c>
       <c r="D194" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="E194" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -6963,10 +6969,10 @@
         <v>46146</v>
       </c>
       <c r="D195" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E195" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -6989,10 +6995,10 @@
         <v>46146</v>
       </c>
       <c r="D196" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="E196" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -7015,10 +7021,10 @@
         <v>46146</v>
       </c>
       <c r="D197" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="E197" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -7041,10 +7047,10 @@
         <v>46147</v>
       </c>
       <c r="D198" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="E198" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="F198" s="2">
         <v>1328000</v>
@@ -7067,10 +7073,10 @@
         <v>46147</v>
       </c>
       <c r="D199" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="E199" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="F199" s="2">
         <v>765000</v>
@@ -7093,10 +7099,10 @@
         <v>46147</v>
       </c>
       <c r="D200" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="E200" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="F200" s="2">
         <v>3600000</v>
@@ -7119,10 +7125,10 @@
         <v>46147</v>
       </c>
       <c r="D201" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="E201" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -7145,10 +7151,10 @@
         <v>46148</v>
       </c>
       <c r="D202" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="E202" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -7171,10 +7177,10 @@
         <v>46150</v>
       </c>
       <c r="D203" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="E203" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -7197,10 +7203,10 @@
         <v>46150</v>
       </c>
       <c r="D204" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="E204" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -7223,10 +7229,10 @@
         <v>46153</v>
       </c>
       <c r="D205" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="E205" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -7249,10 +7255,10 @@
         <v>46153</v>
       </c>
       <c r="D206" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="E206" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="F206" s="2">
         <v>2522500</v>
@@ -7275,10 +7281,10 @@
         <v>46154</v>
       </c>
       <c r="D207" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="E207" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="F207" s="2">
         <v>5024709</v>
@@ -7301,10 +7307,10 @@
         <v>46154</v>
       </c>
       <c r="D208" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="E208" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="F208" s="2">
         <v>188400</v>
@@ -7327,10 +7333,10 @@
         <v>46154</v>
       </c>
       <c r="D209" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="E209" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -7353,10 +7359,10 @@
         <v>46155</v>
       </c>
       <c r="D210" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="E210" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F210" s="2">
         <v>3607000</v>
@@ -7379,10 +7385,10 @@
         <v>46155</v>
       </c>
       <c r="D211" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="E211" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="F211" s="2">
         <v>9814000</v>
@@ -7405,10 +7411,10 @@
         <v>46155</v>
       </c>
       <c r="D212" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="E212" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -7431,10 +7437,10 @@
         <v>46157</v>
       </c>
       <c r="D213" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="E213" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="F213" s="2">
         <v>777000</v>
@@ -7457,10 +7463,10 @@
         <v>46158</v>
       </c>
       <c r="D214" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="E214" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -7483,10 +7489,10 @@
         <v>46162</v>
       </c>
       <c r="D215" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="E215" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="F215" s="2">
         <v>12000000</v>
@@ -7509,10 +7515,10 @@
         <v>46162</v>
       </c>
       <c r="D216" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="E216" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="F216" s="2">
         <v>150000000</v>
@@ -7535,10 +7541,10 @@
         <v>46162</v>
       </c>
       <c r="D217" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="E217" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="F217" s="2">
         <v>10342312</v>
@@ -7561,10 +7567,10 @@
         <v>46163</v>
       </c>
       <c r="D218" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="E218" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="F218" s="2">
         <v>409500</v>
@@ -7587,10 +7593,10 @@
         <v>46163</v>
       </c>
       <c r="D219" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="E219" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -7613,10 +7619,10 @@
         <v>46163</v>
       </c>
       <c r="D220" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="E220" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -7639,10 +7645,10 @@
         <v>46164</v>
       </c>
       <c r="D221" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="E221" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="F221" s="2">
         <v>2545456</v>
@@ -7665,10 +7671,10 @@
         <v>46164</v>
       </c>
       <c r="D222" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="E222" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="F222" s="2">
         <v>528000</v>
@@ -7691,10 +7697,10 @@
         <v>46164</v>
       </c>
       <c r="D223" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="E223" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="F223" s="2">
         <v>200000</v>
@@ -7717,10 +7723,10 @@
         <v>46164</v>
       </c>
       <c r="D224" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="E224" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="F224" s="2">
         <v>800000</v>
@@ -7743,10 +7749,10 @@
         <v>46167</v>
       </c>
       <c r="D225" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="E225" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="F225" s="2">
         <v>1470000</v>
@@ -7769,10 +7775,10 @@
         <v>46167</v>
       </c>
       <c r="D226" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="E226" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="F226" s="2">
         <v>919688</v>
@@ -7795,10 +7801,10 @@
         <v>46168</v>
       </c>
       <c r="D227" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="E227" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="F227" s="2">
         <v>768910</v>
@@ -7821,10 +7827,10 @@
         <v>46171</v>
       </c>
       <c r="D228" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="E228" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -7847,10 +7853,10 @@
         <v>46173</v>
       </c>
       <c r="D229" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="E229" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="F229">
         <v>0</v>
@@ -7873,10 +7879,10 @@
         <v>46173</v>
       </c>
       <c r="D230" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="E230" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -7899,10 +7905,10 @@
         <v>46173</v>
       </c>
       <c r="D231" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="E231" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="F231">
         <v>0</v>

--- a/test1.xlsx
+++ b/test1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Automated-recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F55564A-BD45-4E0F-861B-B67CD94A8698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C131637-6A48-4DE6-B5D0-CF3C1D835A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36" yWindow="744" windowWidth="23004" windowHeight="12216" xr2:uid="{C1D30F33-C917-4DB8-AB4B-FBD71EBDB54C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1D30F33-C917-4DB8-AB4B-FBD71EBDB54C}"/>
   </bookViews>
   <sheets>
     <sheet name="Output File" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="349">
   <si>
     <t>Account-No</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Reference-No</t>
   </si>
   <si>
-    <t>Description / Note</t>
-  </si>
-  <si>
     <t>Debit</t>
   </si>
   <si>
@@ -1075,6 +1072,12 @@
   </si>
   <si>
     <t>ONGKOS KIRIM 221225</t>
+  </si>
+  <si>
+    <t>Catatan</t>
+  </si>
+  <si>
+    <t>Deskripsi</t>
   </si>
 </sst>
 </file>
@@ -1917,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408A0166-60BA-4F1B-A599-DFEB0E649345}">
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:J231"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -1929,7 +1932,7 @@
     <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1940,21 +1943,24 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1966,21 +1972,21 @@
         <v>29080696</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>46031</v>
       </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
       <c r="F3" s="2">
         <v>4884000</v>
@@ -1992,21 +1998,21 @@
         <v>24196696</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
         <v>46037</v>
       </c>
       <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="2">
         <v>127950</v>
@@ -2018,21 +2024,21 @@
         <v>24068746</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1">
         <v>46037</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2">
         <v>1565933</v>
@@ -2044,21 +2050,21 @@
         <v>22502813</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>46037</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
         <v>1293387</v>
@@ -2070,21 +2076,21 @@
         <v>21209426</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>46037</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F7" s="2">
         <v>192800</v>
@@ -2096,21 +2102,21 @@
         <v>21016626</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1">
         <v>46037</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2">
         <v>119000</v>
@@ -2122,21 +2128,21 @@
         <v>20897626</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1">
         <v>46037</v>
       </c>
       <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
         <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2148,21 +2154,21 @@
         <v>21463066</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1">
         <v>46037</v>
       </c>
       <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
         <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2174,21 +2180,21 @@
         <v>22378966</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1">
         <v>46037</v>
       </c>
       <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2200,21 +2206,21 @@
         <v>23674094</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1">
         <v>46037</v>
       </c>
       <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
         <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
       </c>
       <c r="F12" s="2">
         <v>567987</v>
@@ -2226,21 +2232,21 @@
         <v>23106107</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>46037</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" s="2">
         <v>565440</v>
@@ -2252,21 +2258,21 @@
         <v>22540667</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1">
         <v>46037</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="2">
         <v>915900</v>
@@ -2278,21 +2284,21 @@
         <v>21624767</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1">
         <v>46037</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2">
         <v>1295128</v>
@@ -2304,21 +2310,21 @@
         <v>20329639</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>46043</v>
       </c>
       <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
         <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2332,19 +2338,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1">
         <v>46044</v>
       </c>
       <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
         <v>29</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
       </c>
       <c r="F17" s="2">
         <v>600000</v>
@@ -2358,19 +2364,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1">
         <v>46044</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="2">
         <v>1500000</v>
@@ -2384,19 +2390,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="1">
         <v>46044</v>
       </c>
       <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
         <v>31</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2410,19 +2416,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="1">
         <v>46045</v>
       </c>
       <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
         <v>33</v>
-      </c>
-      <c r="E20" t="s">
-        <v>34</v>
       </c>
       <c r="F20" s="2">
         <v>5000000</v>
@@ -2436,19 +2442,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1">
         <v>46048</v>
       </c>
       <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
         <v>35</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2462,19 +2468,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1">
         <v>46049</v>
       </c>
       <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
         <v>37</v>
-      </c>
-      <c r="E22" t="s">
-        <v>38</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2488,19 +2494,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1">
         <v>46051</v>
       </c>
       <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="s">
         <v>39</v>
-      </c>
-      <c r="E23" t="s">
-        <v>40</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2514,19 +2520,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1">
         <v>46052</v>
       </c>
       <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
         <v>41</v>
-      </c>
-      <c r="E24" t="s">
-        <v>42</v>
       </c>
       <c r="F24" s="2">
         <v>1500000</v>
@@ -2540,19 +2546,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1">
         <v>46052</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25" s="2">
         <v>720000</v>
@@ -2566,19 +2572,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1">
         <v>46052</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" s="2">
         <v>17297626</v>
@@ -2592,19 +2598,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1">
         <v>46053</v>
       </c>
       <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" t="s">
         <v>45</v>
-      </c>
-      <c r="E27" t="s">
-        <v>46</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2618,19 +2624,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="1">
         <v>46053</v>
       </c>
       <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
         <v>47</v>
-      </c>
-      <c r="E28" t="s">
-        <v>48</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2644,19 +2650,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="1">
         <v>46053</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2670,19 +2676,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1">
         <v>46053</v>
       </c>
       <c r="D30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" t="s">
         <v>50</v>
-      </c>
-      <c r="E30" t="s">
-        <v>51</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2696,19 +2702,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1">
         <v>46053</v>
       </c>
       <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" t="s">
         <v>52</v>
-      </c>
-      <c r="E31" t="s">
-        <v>53</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2722,19 +2728,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="1">
         <v>46054</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2748,19 +2754,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1">
         <v>46054</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2774,19 +2780,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="1">
         <v>46054</v>
       </c>
       <c r="D34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" t="s">
         <v>55</v>
-      </c>
-      <c r="E34" t="s">
-        <v>56</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2800,19 +2806,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="1">
         <v>46054</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2826,19 +2832,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1">
         <v>46059</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2852,19 +2858,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1">
         <v>46063</v>
       </c>
       <c r="D37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" t="s">
         <v>59</v>
-      </c>
-      <c r="E37" t="s">
-        <v>60</v>
       </c>
       <c r="F37" s="2">
         <v>395000</v>
@@ -2878,19 +2884,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1">
         <v>46063</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="2">
         <v>2400000</v>
@@ -2904,19 +2910,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="1">
         <v>46063</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F39" s="2">
         <v>800000</v>
@@ -2930,19 +2936,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="1">
         <v>46063</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F40" s="2">
         <v>5400000</v>
@@ -2956,19 +2962,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" s="1">
         <v>46065</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F41" s="2">
         <v>640000</v>
@@ -2982,19 +2988,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="1">
         <v>46066</v>
       </c>
       <c r="D42" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" t="s">
         <v>65</v>
-      </c>
-      <c r="E42" t="s">
-        <v>66</v>
       </c>
       <c r="F42" s="2">
         <v>1800000</v>
@@ -3008,19 +3014,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="1">
         <v>46066</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F43" s="2">
         <v>44689266</v>
@@ -3034,19 +3040,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="1">
         <v>46066</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F44" s="2">
         <v>2619000</v>
@@ -3060,19 +3066,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="1">
         <v>46066</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3086,19 +3092,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" s="1">
         <v>46066</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3112,19 +3118,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1">
         <v>46066</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -3138,19 +3144,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1">
         <v>46068</v>
       </c>
       <c r="D48" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
         <v>71</v>
-      </c>
-      <c r="E48" t="s">
-        <v>72</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -3164,19 +3170,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1">
         <v>46068</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -3190,19 +3196,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50" s="1">
         <v>46068</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -3216,19 +3222,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C51" s="1">
         <v>46068</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -3242,19 +3248,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="1">
         <v>46068</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -3268,19 +3274,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C53" s="1">
         <v>46068</v>
       </c>
       <c r="D53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" t="s">
         <v>77</v>
-      </c>
-      <c r="E53" t="s">
-        <v>78</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3294,19 +3300,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54" s="1">
         <v>46068</v>
       </c>
       <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" t="s">
         <v>79</v>
-      </c>
-      <c r="E54" t="s">
-        <v>80</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3320,19 +3326,19 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1">
         <v>46068</v>
       </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F55" s="2">
         <v>627600</v>
@@ -3346,19 +3352,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56" s="1">
         <v>46068</v>
       </c>
       <c r="D56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F56" s="2">
         <v>1830386</v>
@@ -3372,19 +3378,19 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="1">
         <v>46068</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -3398,19 +3404,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" s="1">
         <v>46068</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F58" s="2">
         <v>600000</v>
@@ -3424,19 +3430,19 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" s="1">
         <v>46073</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="2">
         <v>26400000</v>
@@ -3450,19 +3456,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" s="1">
         <v>46078</v>
       </c>
       <c r="D60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" t="s">
         <v>86</v>
-      </c>
-      <c r="E60" t="s">
-        <v>87</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3476,19 +3482,19 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C61" s="1">
         <v>46078</v>
       </c>
       <c r="D61" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" t="s">
         <v>88</v>
-      </c>
-      <c r="E61" t="s">
-        <v>89</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3502,19 +3508,19 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1">
         <v>46080</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F62" s="2">
         <v>2025000</v>
@@ -3528,19 +3534,19 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C63" s="1">
         <v>46081</v>
       </c>
       <c r="D63" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" t="s">
         <v>91</v>
-      </c>
-      <c r="E63" t="s">
-        <v>92</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3554,19 +3560,19 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C64" s="1">
         <v>46081</v>
       </c>
       <c r="D64" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" t="s">
         <v>93</v>
-      </c>
-      <c r="E64" t="s">
-        <v>94</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3580,19 +3586,19 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C65" s="1">
         <v>46081</v>
       </c>
       <c r="D65" t="s">
+        <v>94</v>
+      </c>
+      <c r="E65" t="s">
         <v>95</v>
-      </c>
-      <c r="E65" t="s">
-        <v>96</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3606,19 +3612,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" s="1">
         <v>46081</v>
       </c>
       <c r="D66" t="s">
+        <v>96</v>
+      </c>
+      <c r="E66" t="s">
         <v>97</v>
-      </c>
-      <c r="E66" t="s">
-        <v>98</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3632,19 +3638,19 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1">
         <v>46081</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3658,19 +3664,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="1">
         <v>46081</v>
       </c>
       <c r="D68" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" t="s">
         <v>100</v>
-      </c>
-      <c r="E68" t="s">
-        <v>101</v>
       </c>
       <c r="F68" s="2">
         <v>529823</v>
@@ -3684,19 +3690,19 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" s="1">
         <v>46081</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3710,19 +3716,19 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" s="1">
         <v>46082</v>
       </c>
       <c r="D70" t="s">
+        <v>102</v>
+      </c>
+      <c r="E70" t="s">
         <v>103</v>
-      </c>
-      <c r="E70" t="s">
-        <v>104</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3736,19 +3742,19 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C71" s="1">
         <v>46082</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -3762,19 +3768,19 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C72" s="1">
         <v>46083</v>
       </c>
       <c r="D72" t="s">
+        <v>105</v>
+      </c>
+      <c r="E72" t="s">
         <v>106</v>
-      </c>
-      <c r="E72" t="s">
-        <v>107</v>
       </c>
       <c r="F72" s="2">
         <v>27152154</v>
@@ -3788,19 +3794,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C73" s="1">
         <v>46083</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F73" s="2">
         <v>1831500</v>
@@ -3814,19 +3820,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1">
         <v>46083</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F74" s="2">
         <v>22000000</v>
@@ -3840,19 +3846,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="1">
         <v>46084</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3866,19 +3872,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1">
         <v>46086</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E76" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F76" s="2">
         <v>777000</v>
@@ -3892,19 +3898,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1">
         <v>46086</v>
       </c>
       <c r="D77" t="s">
+        <v>108</v>
+      </c>
+      <c r="E77" t="s">
         <v>109</v>
-      </c>
-      <c r="E77" t="s">
-        <v>110</v>
       </c>
       <c r="F77" s="2">
         <v>675000</v>
@@ -3918,19 +3924,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="1">
         <v>46086</v>
       </c>
       <c r="D78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3944,19 +3950,19 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" s="1">
         <v>46087</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F79" s="2">
         <v>5000000</v>
@@ -3970,19 +3976,19 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="1">
         <v>46087</v>
       </c>
       <c r="D80" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F80" s="2">
         <v>2970500</v>
@@ -3996,19 +4002,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81" s="1">
         <v>46090</v>
       </c>
       <c r="D81" t="s">
+        <v>112</v>
+      </c>
+      <c r="E81" t="s">
         <v>113</v>
-      </c>
-      <c r="E81" t="s">
-        <v>114</v>
       </c>
       <c r="F81" s="2">
         <v>104274954</v>
@@ -4022,19 +4028,19 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="1">
         <v>46090</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F82" s="2">
         <v>3683000</v>
@@ -4048,19 +4054,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="1">
         <v>46090</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E83" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F83" s="2">
         <v>1455000</v>
@@ -4074,19 +4080,19 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84" s="1">
         <v>46090</v>
       </c>
       <c r="D84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4100,19 +4106,19 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="1">
         <v>46090</v>
       </c>
       <c r="D85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E85" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4126,19 +4132,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86" s="1">
         <v>46090</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4152,19 +4158,19 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C87" s="1">
         <v>46091</v>
       </c>
       <c r="D87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E87" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4178,19 +4184,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" s="1">
         <v>46091</v>
       </c>
       <c r="D88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E88" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4204,19 +4210,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C89" s="1">
         <v>46092</v>
       </c>
       <c r="D89" t="s">
+        <v>120</v>
+      </c>
+      <c r="E89" t="s">
         <v>121</v>
-      </c>
-      <c r="E89" t="s">
-        <v>122</v>
       </c>
       <c r="F89" s="2">
         <v>3025000</v>
@@ -4230,19 +4236,19 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C90" s="1">
         <v>46092</v>
       </c>
       <c r="D90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E90" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F90" s="2">
         <v>5500000</v>
@@ -4256,19 +4262,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C91" s="1">
         <v>46092</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -4282,19 +4288,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92" s="1">
         <v>46093</v>
       </c>
       <c r="D92" t="s">
+        <v>123</v>
+      </c>
+      <c r="E92" t="s">
         <v>124</v>
-      </c>
-      <c r="E92" t="s">
-        <v>125</v>
       </c>
       <c r="F92" s="2">
         <v>1221000</v>
@@ -4308,19 +4314,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C93" s="1">
         <v>46093</v>
       </c>
       <c r="D93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E93" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F93" s="2">
         <v>12272727</v>
@@ -4334,19 +4340,19 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94" s="1">
         <v>46093</v>
       </c>
       <c r="D94" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E94" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4360,19 +4366,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="1">
         <v>46093</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E95" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4386,19 +4392,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C96" s="1">
         <v>46093</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E96" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F96" s="2">
         <v>23333</v>
@@ -4412,19 +4418,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" s="1">
         <v>46093</v>
       </c>
       <c r="D97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -4438,19 +4444,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C98" s="1">
         <v>46094</v>
       </c>
       <c r="D98" t="s">
+        <v>129</v>
+      </c>
+      <c r="E98" t="s">
         <v>130</v>
-      </c>
-      <c r="E98" t="s">
-        <v>131</v>
       </c>
       <c r="F98" s="2">
         <v>12903612</v>
@@ -4464,19 +4470,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C99" s="1">
         <v>46094</v>
       </c>
       <c r="D99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F99" s="2">
         <v>920000</v>
@@ -4490,19 +4496,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100" s="1">
         <v>46096</v>
       </c>
       <c r="D100" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E100" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -4516,19 +4522,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B101" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C101" s="1">
         <v>46097</v>
       </c>
       <c r="D101" t="s">
+        <v>132</v>
+      </c>
+      <c r="E101" t="s">
         <v>133</v>
-      </c>
-      <c r="E101" t="s">
-        <v>134</v>
       </c>
       <c r="F101" s="2">
         <v>5070885</v>
@@ -4542,19 +4548,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102" s="1">
         <v>46097</v>
       </c>
       <c r="D102" t="s">
+        <v>134</v>
+      </c>
+      <c r="E102" t="s">
         <v>135</v>
-      </c>
-      <c r="E102" t="s">
-        <v>136</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4568,19 +4574,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103" s="1">
         <v>46098</v>
       </c>
       <c r="D103" t="s">
+        <v>136</v>
+      </c>
+      <c r="E103" t="s">
         <v>137</v>
-      </c>
-      <c r="E103" t="s">
-        <v>138</v>
       </c>
       <c r="F103" s="2">
         <v>5427000</v>
@@ -4594,19 +4600,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104" s="1">
         <v>46098</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F104" s="2">
         <v>4401463</v>
@@ -4620,19 +4626,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C105" s="1">
         <v>46098</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F105" s="2">
         <v>2261500</v>
@@ -4646,19 +4652,19 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106" s="1">
         <v>46098</v>
       </c>
       <c r="D106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E106" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F106" s="2">
         <v>660000</v>
@@ -4672,19 +4678,19 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C107" s="1">
         <v>46098</v>
       </c>
       <c r="D107" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E107" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F107" s="2">
         <v>2430000</v>
@@ -4698,19 +4704,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108" s="1">
         <v>46098</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E108" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F108" s="2">
         <v>665000</v>
@@ -4724,19 +4730,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C109" s="1">
         <v>46098</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E109" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F109" s="2">
         <v>26609111</v>
@@ -4750,19 +4756,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110" s="1">
         <v>46101</v>
       </c>
       <c r="D110" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E110" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -4776,19 +4782,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B111" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C111" s="1">
         <v>46105</v>
       </c>
       <c r="D111" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -4802,19 +4808,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112" s="1">
         <v>46105</v>
       </c>
       <c r="D112" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -4828,19 +4834,19 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B113" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C113" s="1">
         <v>46105</v>
       </c>
       <c r="D113" t="s">
+        <v>146</v>
+      </c>
+      <c r="E113" t="s">
         <v>147</v>
-      </c>
-      <c r="E113" t="s">
-        <v>148</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -4854,19 +4860,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C114" s="1">
         <v>46105</v>
       </c>
       <c r="D114" t="s">
+        <v>148</v>
+      </c>
+      <c r="E114" t="s">
         <v>149</v>
-      </c>
-      <c r="E114" t="s">
-        <v>150</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -4880,19 +4886,19 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B115" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C115" s="1">
         <v>46105</v>
       </c>
       <c r="D115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -4906,19 +4912,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116" s="1">
         <v>46105</v>
       </c>
       <c r="D116" t="s">
+        <v>151</v>
+      </c>
+      <c r="E116" t="s">
         <v>152</v>
-      </c>
-      <c r="E116" t="s">
-        <v>153</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -4932,19 +4938,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="1">
         <v>46105</v>
       </c>
       <c r="D117" t="s">
+        <v>153</v>
+      </c>
+      <c r="E117" t="s">
         <v>154</v>
-      </c>
-      <c r="E117" t="s">
-        <v>155</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -4958,19 +4964,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="1">
         <v>46105</v>
       </c>
       <c r="D118" t="s">
+        <v>155</v>
+      </c>
+      <c r="E118" t="s">
         <v>156</v>
-      </c>
-      <c r="E118" t="s">
-        <v>157</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -4984,19 +4990,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119" s="1">
         <v>46105</v>
       </c>
       <c r="D119" t="s">
+        <v>157</v>
+      </c>
+      <c r="E119" t="s">
         <v>158</v>
-      </c>
-      <c r="E119" t="s">
-        <v>159</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -5010,19 +5016,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120" s="1">
         <v>46105</v>
       </c>
       <c r="D120" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E120" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -5036,19 +5042,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121" s="1">
         <v>46105</v>
       </c>
       <c r="D121" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E121" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -5062,19 +5068,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122" s="1">
         <v>46105</v>
       </c>
       <c r="D122" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E122" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -5088,19 +5094,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B123" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" s="1">
         <v>46105</v>
       </c>
       <c r="D123" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E123" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F123" s="2">
         <v>1200000</v>
@@ -5114,19 +5120,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C124" s="1">
         <v>46105</v>
       </c>
       <c r="D124" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E124" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F124" s="2">
         <v>1407500</v>
@@ -5140,19 +5146,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C125" s="1">
         <v>46105</v>
       </c>
       <c r="D125" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E125" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F125" s="2">
         <v>800000</v>
@@ -5166,19 +5172,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126" s="1">
         <v>46105</v>
       </c>
       <c r="D126" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E126" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F126" s="2">
         <v>409500</v>
@@ -5192,19 +5198,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C127" s="1">
         <v>46105</v>
       </c>
       <c r="D127" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F127" s="2">
         <v>777000</v>
@@ -5218,19 +5224,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128" s="1">
         <v>46105</v>
       </c>
       <c r="D128" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F128" s="2">
         <v>1255200</v>
@@ -5244,19 +5250,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B129" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C129" s="1">
         <v>46105</v>
       </c>
       <c r="D129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E129" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F129" s="2">
         <v>539251</v>
@@ -5270,19 +5276,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B130" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C130" s="1">
         <v>46105</v>
       </c>
       <c r="D130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E130" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F130" s="2">
         <v>524500</v>
@@ -5296,19 +5302,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B131" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C131" s="1">
         <v>46108</v>
       </c>
       <c r="D131" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E131" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F131" s="2">
         <v>800000</v>
@@ -5322,19 +5328,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B132" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C132" s="1">
         <v>46108</v>
       </c>
       <c r="D132" t="s">
+        <v>167</v>
+      </c>
+      <c r="E132" t="s">
         <v>168</v>
-      </c>
-      <c r="E132" t="s">
-        <v>169</v>
       </c>
       <c r="F132" s="2">
         <v>8500000</v>
@@ -5348,19 +5354,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B133" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C133" s="1">
         <v>46108</v>
       </c>
       <c r="D133" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E133" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F133" s="2">
         <v>2958000</v>
@@ -5374,19 +5380,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134" s="1">
         <v>46108</v>
       </c>
       <c r="D134" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E134" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F134" s="2">
         <v>2800000</v>
@@ -5400,19 +5406,19 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C135" s="1">
         <v>46111</v>
       </c>
       <c r="D135" t="s">
+        <v>170</v>
+      </c>
+      <c r="E135" t="s">
         <v>171</v>
-      </c>
-      <c r="E135" t="s">
-        <v>172</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -5426,19 +5432,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C136" s="1">
         <v>46111</v>
       </c>
       <c r="D136" t="s">
+        <v>172</v>
+      </c>
+      <c r="E136" t="s">
         <v>173</v>
-      </c>
-      <c r="E136" t="s">
-        <v>174</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -5452,19 +5458,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1">
         <v>46111</v>
       </c>
       <c r="D137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E137" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -5478,19 +5484,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138" s="1">
         <v>46112</v>
       </c>
       <c r="D138" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E138" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -5504,19 +5510,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1">
         <v>46112</v>
       </c>
       <c r="D139" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -5530,19 +5536,19 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1">
         <v>46112</v>
       </c>
       <c r="D140" t="s">
+        <v>177</v>
+      </c>
+      <c r="E140" t="s">
         <v>178</v>
-      </c>
-      <c r="E140" t="s">
-        <v>179</v>
       </c>
       <c r="F140" s="2">
         <v>11737877</v>
@@ -5556,19 +5562,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B141" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C141" s="1">
         <v>46112</v>
       </c>
       <c r="D141" t="s">
+        <v>179</v>
+      </c>
+      <c r="E141" t="s">
         <v>180</v>
-      </c>
-      <c r="E141" t="s">
-        <v>181</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -5582,19 +5588,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C142" s="1">
         <v>46112</v>
       </c>
       <c r="D142" t="s">
+        <v>181</v>
+      </c>
+      <c r="E142" t="s">
         <v>182</v>
-      </c>
-      <c r="E142" t="s">
-        <v>183</v>
       </c>
       <c r="F142" s="2">
         <v>1020600</v>
@@ -5608,19 +5614,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C143" s="1">
         <v>46112</v>
       </c>
       <c r="D143" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E143" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F143" s="2">
         <v>800000</v>
@@ -5634,19 +5640,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C144" s="1">
         <v>46112</v>
       </c>
       <c r="D144" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E144" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F144" s="2">
         <v>600000</v>
@@ -5660,19 +5666,19 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C145" s="1">
         <v>46113</v>
       </c>
       <c r="D145" t="s">
+        <v>184</v>
+      </c>
+      <c r="E145" t="s">
         <v>185</v>
-      </c>
-      <c r="E145" t="s">
-        <v>186</v>
       </c>
       <c r="F145" s="2">
         <v>730239</v>
@@ -5686,19 +5692,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C146" s="1">
         <v>46113</v>
       </c>
       <c r="D146" t="s">
+        <v>186</v>
+      </c>
+      <c r="E146" t="s">
         <v>187</v>
-      </c>
-      <c r="E146" t="s">
-        <v>188</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -5712,19 +5718,19 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C147" s="1">
         <v>46113</v>
       </c>
       <c r="D147" t="s">
+        <v>188</v>
+      </c>
+      <c r="E147" t="s">
         <v>189</v>
-      </c>
-      <c r="E147" t="s">
-        <v>190</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -5738,19 +5744,19 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C148" s="1">
         <v>46115</v>
       </c>
       <c r="D148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E148" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F148" s="2">
         <v>150000000</v>
@@ -5764,19 +5770,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C149" s="1">
         <v>46118</v>
       </c>
       <c r="D149" t="s">
+        <v>191</v>
+      </c>
+      <c r="E149" t="s">
         <v>192</v>
-      </c>
-      <c r="E149" t="s">
-        <v>193</v>
       </c>
       <c r="F149" s="2">
         <v>4292996</v>
@@ -5790,19 +5796,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C150" s="1">
         <v>46118</v>
       </c>
       <c r="D150" t="s">
+        <v>193</v>
+      </c>
+      <c r="E150" t="s">
         <v>194</v>
-      </c>
-      <c r="E150" t="s">
-        <v>195</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -5816,19 +5822,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C151" s="1">
         <v>46118</v>
       </c>
       <c r="D151" t="s">
+        <v>195</v>
+      </c>
+      <c r="E151" t="s">
         <v>196</v>
-      </c>
-      <c r="E151" t="s">
-        <v>197</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -5842,19 +5848,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C152" s="1">
         <v>46118</v>
       </c>
       <c r="D152" t="s">
+        <v>197</v>
+      </c>
+      <c r="E152" t="s">
         <v>198</v>
-      </c>
-      <c r="E152" t="s">
-        <v>199</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -5868,19 +5874,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C153" s="1">
         <v>46119</v>
       </c>
       <c r="D153" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E153" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F153" s="2">
         <v>4810000</v>
@@ -5894,19 +5900,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C154" s="1">
         <v>46119</v>
       </c>
       <c r="D154" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F154" s="2">
         <v>5916000</v>
@@ -5920,19 +5926,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C155" s="1">
         <v>46119</v>
       </c>
       <c r="D155" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E155" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F155" s="2">
         <v>10000000</v>
@@ -5946,19 +5952,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C156" s="1">
         <v>46119</v>
       </c>
       <c r="D156" t="s">
+        <v>200</v>
+      </c>
+      <c r="E156" t="s">
         <v>201</v>
-      </c>
-      <c r="E156" t="s">
-        <v>202</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -5972,19 +5978,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C157" s="1">
         <v>46119</v>
       </c>
       <c r="D157" t="s">
+        <v>202</v>
+      </c>
+      <c r="E157" t="s">
         <v>203</v>
-      </c>
-      <c r="E157" t="s">
-        <v>204</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -5998,19 +6004,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B158" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C158" s="1">
         <v>46119</v>
       </c>
       <c r="D158" t="s">
+        <v>204</v>
+      </c>
+      <c r="E158" t="s">
         <v>205</v>
-      </c>
-      <c r="E158" t="s">
-        <v>206</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6024,19 +6030,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C159" s="1">
         <v>46120</v>
       </c>
       <c r="D159" t="s">
+        <v>206</v>
+      </c>
+      <c r="E159" t="s">
         <v>207</v>
-      </c>
-      <c r="E159" t="s">
-        <v>208</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -6050,19 +6056,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B160" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C160" s="1">
         <v>46121</v>
       </c>
       <c r="D160" t="s">
+        <v>208</v>
+      </c>
+      <c r="E160" t="s">
         <v>209</v>
-      </c>
-      <c r="E160" t="s">
-        <v>210</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -6076,19 +6082,19 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B161" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C161" s="1">
         <v>46122</v>
       </c>
       <c r="D161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E161" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F161" s="2">
         <v>13800000</v>
@@ -6102,19 +6108,19 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C162" s="1">
         <v>46122</v>
       </c>
       <c r="D162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E162" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F162" s="2">
         <v>300000</v>
@@ -6128,19 +6134,19 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B163" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C163" s="1">
         <v>46123</v>
       </c>
       <c r="D163" t="s">
+        <v>211</v>
+      </c>
+      <c r="E163" t="s">
         <v>212</v>
-      </c>
-      <c r="E163" t="s">
-        <v>213</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -6154,19 +6160,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C164" s="1">
         <v>46125</v>
       </c>
       <c r="D164" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E164" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -6180,19 +6186,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B165" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C165" s="1">
         <v>46125</v>
       </c>
       <c r="D165" t="s">
+        <v>214</v>
+      </c>
+      <c r="E165" t="s">
         <v>215</v>
-      </c>
-      <c r="E165" t="s">
-        <v>216</v>
       </c>
       <c r="F165" s="2">
         <v>500000</v>
@@ -6206,19 +6212,19 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C166" s="1">
         <v>46125</v>
       </c>
       <c r="D166" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E166" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F166" s="2">
         <v>739000</v>
@@ -6232,19 +6238,19 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C167" s="1">
         <v>46125</v>
       </c>
       <c r="D167" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E167" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F167" s="2">
         <v>1800000</v>
@@ -6258,19 +6264,19 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C168" s="1">
         <v>46125</v>
       </c>
       <c r="D168" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E168" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F168" s="2">
         <v>1341600</v>
@@ -6284,19 +6290,19 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C169" s="1">
         <v>46126</v>
       </c>
       <c r="D169" t="s">
+        <v>219</v>
+      </c>
+      <c r="E169" t="s">
         <v>220</v>
-      </c>
-      <c r="E169" t="s">
-        <v>221</v>
       </c>
       <c r="F169" s="2">
         <v>2156250</v>
@@ -6310,19 +6316,19 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C170" s="1">
         <v>46127</v>
       </c>
       <c r="D170" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E170" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F170" s="2">
         <v>1075000</v>
@@ -6336,19 +6342,19 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C171" s="1">
         <v>46127</v>
       </c>
       <c r="D171" t="s">
+        <v>221</v>
+      </c>
+      <c r="E171" t="s">
         <v>222</v>
-      </c>
-      <c r="E171" t="s">
-        <v>223</v>
       </c>
       <c r="F171" s="2">
         <v>409500</v>
@@ -6362,19 +6368,19 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C172" s="1">
         <v>46127</v>
       </c>
       <c r="D172" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E172" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F172" s="2">
         <v>203800</v>
@@ -6388,19 +6394,19 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C173" s="1">
         <v>46128</v>
       </c>
       <c r="D173" t="s">
+        <v>223</v>
+      </c>
+      <c r="E173" t="s">
         <v>224</v>
-      </c>
-      <c r="E173" t="s">
-        <v>225</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -6414,19 +6420,19 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C174" s="1">
         <v>46128</v>
       </c>
       <c r="D174" t="s">
+        <v>225</v>
+      </c>
+      <c r="E174" t="s">
         <v>226</v>
-      </c>
-      <c r="E174" t="s">
-        <v>227</v>
       </c>
       <c r="F174" s="2">
         <v>810000</v>
@@ -6440,19 +6446,19 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C175" s="1">
         <v>46129</v>
       </c>
       <c r="D175" t="s">
+        <v>227</v>
+      </c>
+      <c r="E175" t="s">
         <v>228</v>
-      </c>
-      <c r="E175" t="s">
-        <v>229</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -6466,19 +6472,19 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C176" s="1">
         <v>46129</v>
       </c>
       <c r="D176" t="s">
+        <v>229</v>
+      </c>
+      <c r="E176" t="s">
         <v>230</v>
-      </c>
-      <c r="E176" t="s">
-        <v>231</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -6492,19 +6498,19 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C177" s="1">
         <v>46131</v>
       </c>
       <c r="D177" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E177" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -6518,19 +6524,19 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C178" s="1">
         <v>46133</v>
       </c>
       <c r="D178" t="s">
+        <v>232</v>
+      </c>
+      <c r="E178" t="s">
         <v>233</v>
-      </c>
-      <c r="E178" t="s">
-        <v>234</v>
       </c>
       <c r="F178" s="2">
         <v>1200000</v>
@@ -6544,19 +6550,19 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C179" s="1">
         <v>46133</v>
       </c>
       <c r="D179" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E179" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F179" s="2">
         <v>2430000</v>
@@ -6570,19 +6576,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B180" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C180" s="1">
         <v>46133</v>
       </c>
       <c r="D180" t="s">
+        <v>235</v>
+      </c>
+      <c r="E180" t="s">
         <v>236</v>
-      </c>
-      <c r="E180" t="s">
-        <v>237</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -6596,19 +6602,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B181" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C181" s="1">
         <v>46134</v>
       </c>
       <c r="D181" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -6622,19 +6628,19 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C182" s="1">
         <v>46134</v>
       </c>
       <c r="D182" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E182" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -6648,19 +6654,19 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B183" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C183" s="1">
         <v>46135</v>
       </c>
       <c r="D183" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E183" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -6674,19 +6680,19 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B184" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C184" s="1">
         <v>46136</v>
       </c>
       <c r="D184" t="s">
+        <v>240</v>
+      </c>
+      <c r="E184" t="s">
         <v>241</v>
-      </c>
-      <c r="E184" t="s">
-        <v>242</v>
       </c>
       <c r="F184" s="2">
         <v>2952761</v>
@@ -6700,19 +6706,19 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B185" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C185" s="1">
         <v>46140</v>
       </c>
       <c r="D185" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E185" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F185" s="2">
         <v>1000000</v>
@@ -6726,19 +6732,19 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B186" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C186" s="1">
         <v>46141</v>
       </c>
       <c r="D186" t="s">
+        <v>243</v>
+      </c>
+      <c r="E186" t="s">
         <v>244</v>
-      </c>
-      <c r="E186" t="s">
-        <v>245</v>
       </c>
       <c r="F186" s="2">
         <v>13888862</v>
@@ -6752,19 +6758,19 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B187" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C187" s="1">
         <v>46141</v>
       </c>
       <c r="D187" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E187" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F187" s="2">
         <v>1470000</v>
@@ -6778,19 +6784,19 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B188" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C188" s="1">
         <v>46141</v>
       </c>
       <c r="D188" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E188" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F188" s="2">
         <v>1470000</v>
@@ -6804,19 +6810,19 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B189" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C189" s="1">
         <v>46142</v>
       </c>
       <c r="D189" t="s">
+        <v>247</v>
+      </c>
+      <c r="E189" t="s">
         <v>248</v>
-      </c>
-      <c r="E189" t="s">
-        <v>249</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -6830,19 +6836,19 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B190" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C190" s="1">
         <v>46142</v>
       </c>
       <c r="D190" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E190" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F190" s="2">
         <v>35200000</v>
@@ -6856,19 +6862,19 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B191" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C191" s="1">
         <v>46142</v>
       </c>
       <c r="D191" t="s">
+        <v>250</v>
+      </c>
+      <c r="E191" t="s">
         <v>251</v>
-      </c>
-      <c r="E191" t="s">
-        <v>252</v>
       </c>
       <c r="F191" s="2">
         <v>12903612</v>
@@ -6882,19 +6888,19 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B192" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C192" s="1">
         <v>46142</v>
       </c>
       <c r="D192" t="s">
+        <v>252</v>
+      </c>
+      <c r="E192" t="s">
         <v>253</v>
-      </c>
-      <c r="E192" t="s">
-        <v>254</v>
       </c>
       <c r="F192">
         <v>0</v>
@@ -6908,19 +6914,19 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B193" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C193" s="1">
         <v>46142</v>
       </c>
       <c r="D193" t="s">
+        <v>254</v>
+      </c>
+      <c r="E193" t="s">
         <v>255</v>
-      </c>
-      <c r="E193" t="s">
-        <v>256</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -6934,19 +6940,19 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B194" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C194" s="1">
         <v>46143</v>
       </c>
       <c r="D194" t="s">
+        <v>256</v>
+      </c>
+      <c r="E194" t="s">
         <v>257</v>
-      </c>
-      <c r="E194" t="s">
-        <v>258</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -6960,19 +6966,19 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B195" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C195" s="1">
         <v>46146</v>
       </c>
       <c r="D195" t="s">
+        <v>258</v>
+      </c>
+      <c r="E195" t="s">
         <v>259</v>
-      </c>
-      <c r="E195" t="s">
-        <v>260</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -6986,19 +6992,19 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B196" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C196" s="1">
         <v>46146</v>
       </c>
       <c r="D196" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E196" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -7012,19 +7018,19 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B197" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C197" s="1">
         <v>46146</v>
       </c>
       <c r="D197" t="s">
+        <v>261</v>
+      </c>
+      <c r="E197" t="s">
         <v>262</v>
-      </c>
-      <c r="E197" t="s">
-        <v>263</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -7038,19 +7044,19 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B198" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C198" s="1">
         <v>46147</v>
       </c>
       <c r="D198" t="s">
+        <v>263</v>
+      </c>
+      <c r="E198" t="s">
         <v>264</v>
-      </c>
-      <c r="E198" t="s">
-        <v>265</v>
       </c>
       <c r="F198" s="2">
         <v>1328000</v>
@@ -7064,19 +7070,19 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B199" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C199" s="1">
         <v>46147</v>
       </c>
       <c r="D199" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E199" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F199" s="2">
         <v>765000</v>
@@ -7090,19 +7096,19 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B200" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C200" s="1">
         <v>46147</v>
       </c>
       <c r="D200" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E200" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F200" s="2">
         <v>3600000</v>
@@ -7116,19 +7122,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B201" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C201" s="1">
         <v>46147</v>
       </c>
       <c r="D201" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E201" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -7142,19 +7148,19 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B202" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C202" s="1">
         <v>46148</v>
       </c>
       <c r="D202" t="s">
+        <v>268</v>
+      </c>
+      <c r="E202" t="s">
         <v>269</v>
-      </c>
-      <c r="E202" t="s">
-        <v>270</v>
       </c>
       <c r="F202">
         <v>0</v>
@@ -7168,19 +7174,19 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B203" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C203" s="1">
         <v>46150</v>
       </c>
       <c r="D203" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E203" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -7194,19 +7200,19 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B204" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C204" s="1">
         <v>46150</v>
       </c>
       <c r="D204" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E204" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -7220,19 +7226,19 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B205" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C205" s="1">
         <v>46153</v>
       </c>
       <c r="D205" t="s">
+        <v>272</v>
+      </c>
+      <c r="E205" t="s">
         <v>273</v>
-      </c>
-      <c r="E205" t="s">
-        <v>274</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -7246,19 +7252,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B206" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C206" s="1">
         <v>46153</v>
       </c>
       <c r="D206" t="s">
+        <v>274</v>
+      </c>
+      <c r="E206" t="s">
         <v>275</v>
-      </c>
-      <c r="E206" t="s">
-        <v>276</v>
       </c>
       <c r="F206" s="2">
         <v>2522500</v>
@@ -7272,19 +7278,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B207" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C207" s="1">
         <v>46154</v>
       </c>
       <c r="D207" t="s">
+        <v>276</v>
+      </c>
+      <c r="E207" t="s">
         <v>277</v>
-      </c>
-      <c r="E207" t="s">
-        <v>278</v>
       </c>
       <c r="F207" s="2">
         <v>5024709</v>
@@ -7298,19 +7304,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B208" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C208" s="1">
         <v>46154</v>
       </c>
       <c r="D208" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F208" s="2">
         <v>188400</v>
@@ -7324,19 +7330,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B209" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C209" s="1">
         <v>46154</v>
       </c>
       <c r="D209" t="s">
+        <v>278</v>
+      </c>
+      <c r="E209" t="s">
         <v>279</v>
-      </c>
-      <c r="E209" t="s">
-        <v>280</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -7350,19 +7356,19 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B210" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C210" s="1">
         <v>46155</v>
       </c>
       <c r="D210" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E210" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F210" s="2">
         <v>3607000</v>
@@ -7376,19 +7382,19 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B211" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C211" s="1">
         <v>46155</v>
       </c>
       <c r="D211" t="s">
+        <v>280</v>
+      </c>
+      <c r="E211" t="s">
         <v>281</v>
-      </c>
-      <c r="E211" t="s">
-        <v>282</v>
       </c>
       <c r="F211" s="2">
         <v>9814000</v>
@@ -7402,19 +7408,19 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B212" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C212" s="1">
         <v>46155</v>
       </c>
       <c r="D212" t="s">
+        <v>282</v>
+      </c>
+      <c r="E212" t="s">
         <v>283</v>
-      </c>
-      <c r="E212" t="s">
-        <v>284</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -7428,19 +7434,19 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B213" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C213" s="1">
         <v>46157</v>
       </c>
       <c r="D213" t="s">
+        <v>284</v>
+      </c>
+      <c r="E213" t="s">
         <v>285</v>
-      </c>
-      <c r="E213" t="s">
-        <v>286</v>
       </c>
       <c r="F213" s="2">
         <v>777000</v>
@@ -7454,19 +7460,19 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B214" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C214" s="1">
         <v>46158</v>
       </c>
       <c r="D214" t="s">
+        <v>286</v>
+      </c>
+      <c r="E214" t="s">
         <v>287</v>
-      </c>
-      <c r="E214" t="s">
-        <v>288</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -7480,19 +7486,19 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B215" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C215" s="1">
         <v>46162</v>
       </c>
       <c r="D215" t="s">
+        <v>288</v>
+      </c>
+      <c r="E215" t="s">
         <v>289</v>
-      </c>
-      <c r="E215" t="s">
-        <v>290</v>
       </c>
       <c r="F215" s="2">
         <v>12000000</v>
@@ -7506,19 +7512,19 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B216" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C216" s="1">
         <v>46162</v>
       </c>
       <c r="D216" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E216" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F216" s="2">
         <v>150000000</v>
@@ -7532,19 +7538,19 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B217" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C217" s="1">
         <v>46162</v>
       </c>
       <c r="D217" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E217" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F217" s="2">
         <v>10342312</v>
@@ -7558,19 +7564,19 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B218" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C218" s="1">
         <v>46163</v>
       </c>
       <c r="D218" t="s">
+        <v>292</v>
+      </c>
+      <c r="E218" t="s">
         <v>293</v>
-      </c>
-      <c r="E218" t="s">
-        <v>294</v>
       </c>
       <c r="F218" s="2">
         <v>409500</v>
@@ -7584,19 +7590,19 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B219" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C219" s="1">
         <v>46163</v>
       </c>
       <c r="D219" t="s">
+        <v>294</v>
+      </c>
+      <c r="E219" t="s">
         <v>295</v>
-      </c>
-      <c r="E219" t="s">
-        <v>296</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -7610,19 +7616,19 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B220" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C220" s="1">
         <v>46163</v>
       </c>
       <c r="D220" t="s">
+        <v>296</v>
+      </c>
+      <c r="E220" t="s">
         <v>297</v>
-      </c>
-      <c r="E220" t="s">
-        <v>298</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -7636,19 +7642,19 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B221" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C221" s="1">
         <v>46164</v>
       </c>
       <c r="D221" t="s">
+        <v>298</v>
+      </c>
+      <c r="E221" t="s">
         <v>299</v>
-      </c>
-      <c r="E221" t="s">
-        <v>300</v>
       </c>
       <c r="F221" s="2">
         <v>2545456</v>
@@ -7662,19 +7668,19 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B222" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C222" s="1">
         <v>46164</v>
       </c>
       <c r="D222" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E222" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F222" s="2">
         <v>528000</v>
@@ -7688,19 +7694,19 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B223" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C223" s="1">
         <v>46164</v>
       </c>
       <c r="D223" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E223" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F223" s="2">
         <v>200000</v>
@@ -7714,19 +7720,19 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B224" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C224" s="1">
         <v>46164</v>
       </c>
       <c r="D224" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E224" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F224" s="2">
         <v>800000</v>
@@ -7740,19 +7746,19 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B225" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C225" s="1">
         <v>46167</v>
       </c>
       <c r="D225" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E225" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F225" s="2">
         <v>1470000</v>
@@ -7766,19 +7772,19 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B226" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C226" s="1">
         <v>46167</v>
       </c>
       <c r="D226" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E226" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F226" s="2">
         <v>919688</v>
@@ -7792,19 +7798,19 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B227" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C227" s="1">
         <v>46168</v>
       </c>
       <c r="D227" t="s">
+        <v>303</v>
+      </c>
+      <c r="E227" t="s">
         <v>304</v>
-      </c>
-      <c r="E227" t="s">
-        <v>305</v>
       </c>
       <c r="F227" s="2">
         <v>768910</v>
@@ -7818,19 +7824,19 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B228" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C228" s="1">
         <v>46171</v>
       </c>
       <c r="D228" t="s">
+        <v>305</v>
+      </c>
+      <c r="E228" t="s">
         <v>306</v>
-      </c>
-      <c r="E228" t="s">
-        <v>307</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -7844,19 +7850,19 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B229" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C229" s="1">
         <v>46173</v>
       </c>
       <c r="D229" t="s">
+        <v>307</v>
+      </c>
+      <c r="E229" t="s">
         <v>308</v>
-      </c>
-      <c r="E229" t="s">
-        <v>309</v>
       </c>
       <c r="F229">
         <v>0</v>
@@ -7870,19 +7876,19 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B230" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C230" s="1">
         <v>46173</v>
       </c>
       <c r="D230" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E230" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -7896,19 +7902,19 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B231" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C231" s="1">
         <v>46173</v>
       </c>
       <c r="D231" t="s">
+        <v>310</v>
+      </c>
+      <c r="E231" t="s">
         <v>311</v>
-      </c>
-      <c r="E231" t="s">
-        <v>312</v>
       </c>
       <c r="F231">
         <v>0</v>

--- a/test1.xlsx
+++ b/test1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Automated-recon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C131637-6A48-4DE6-B5D0-CF3C1D835A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4389A6-8683-4D09-9605-32FAA3FC147B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1D30F33-C917-4DB8-AB4B-FBD71EBDB54C}"/>
+    <workbookView xWindow="36" yWindow="744" windowWidth="23004" windowHeight="12216" xr2:uid="{C1D30F33-C917-4DB8-AB4B-FBD71EBDB54C}"/>
   </bookViews>
   <sheets>
     <sheet name="Output File" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="350">
   <si>
     <t>Account-No</t>
   </si>
@@ -1078,6 +1078,9 @@
   </si>
   <si>
     <t>Deskripsi</t>
+  </si>
+  <si>
+    <t>double?</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{408A0166-60BA-4F1B-A599-DFEB0E649345}">
-  <dimension ref="A1:J231"/>
+  <dimension ref="A1:K234"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -1932,7 +1935,7 @@
     <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1957,8 +1960,11 @@
       <c r="J1" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
         <v>312</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>29080696</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1998,7 +2004,7 @@
         <v>24196696</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2024,7 +2030,7 @@
         <v>24068746</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2050,7 +2056,7 @@
         <v>22502813</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2076,7 +2082,7 @@
         <v>21209426</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2102,7 +2108,7 @@
         <v>21016626</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2128,7 +2134,7 @@
         <v>20897626</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2154,7 +2160,7 @@
         <v>21463066</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -2180,7 +2186,7 @@
         <v>22378966</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2206,7 +2212,7 @@
         <v>23674094</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -2232,7 +2238,7 @@
         <v>23106107</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -2258,7 +2264,7 @@
         <v>22540667</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -2284,7 +2290,7 @@
         <v>21624767</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -2310,7 +2316,7 @@
         <v>20329639</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -7924,6 +7930,75 @@
       </c>
       <c r="H231" s="2">
         <v>116947843</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>6</v>
+      </c>
+      <c r="B232" t="s">
+        <v>7</v>
+      </c>
+      <c r="C232" s="1">
+        <v>46031</v>
+      </c>
+      <c r="D232" t="s">
+        <v>8</v>
+      </c>
+      <c r="E232" t="s">
+        <v>9</v>
+      </c>
+      <c r="F232" s="2">
+        <v>4884000</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>6</v>
+      </c>
+      <c r="B233" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" s="1">
+        <v>46031</v>
+      </c>
+      <c r="D233" t="s">
+        <v>8</v>
+      </c>
+      <c r="E233" t="s">
+        <v>9</v>
+      </c>
+      <c r="F233" s="2">
+        <v>4884000</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" t="s">
+        <v>7</v>
+      </c>
+      <c r="C234" s="1">
+        <v>46031</v>
+      </c>
+      <c r="D234" t="s">
+        <v>8</v>
+      </c>
+      <c r="E234" t="s">
+        <v>9</v>
+      </c>
+      <c r="F234" s="2">
+        <v>4884000</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
